--- a/2_analysis/ground_truth_full.xlsx
+++ b/2_analysis/ground_truth_full.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>article id</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -449,7 +449,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Legality Constitutionality and jurisprudence</t>
+          <t>Legality, constitutionality and jurisprudence</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
